--- a/outputs/missing_values.xlsx
+++ b/outputs/missing_values.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,11 +1138,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EX-202601-MA-19</t>
+          <t>EX-202606-MA-03</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46028</v>
+        <v>46177</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Korean Air</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>802000</v>
+        <v>765000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1169,45 +1169,45 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M102</t>
+          <t>M110</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>data\inbox\2026-01_marketing_expenses.xlsx</t>
+          <t>data\inbox\2026-06_marketing_expenses.csv</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EX-202601-OP-01</t>
+          <t>EX-202606-MA-18</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46037</v>
+        <v>46189</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fast Campus</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1619000</v>
+        <v>371000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1216,45 +1216,45 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O142</t>
+          <t>M113</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>data\inbox\2026-01_operations_expenses.xlsx</t>
+          <t>data\inbox\2026-06_marketing_expenses.csv</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EX-202602-SA-11</t>
+          <t>EX-202606-OP-15</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46078</v>
+        <v>46174</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DataCloud Korea</t>
+          <t>Fast Campus</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>373000</v>
+        <v>1390000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1263,45 +1263,45 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>S133</t>
+          <t>O146</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
+          <t>data\inbox\2026-06_operations_expenses.csv</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EX-202602-SA-14</t>
+          <t>EX-202601-MA-19</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46059</v>
+        <v>46028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DataCloud Korea</t>
+          <t>Korean Air</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>452000</v>
+        <v>802000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1310,45 +1310,45 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S129</t>
+          <t>M102</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
+          <t>data\inbox\2026-01_marketing_expenses.xlsx</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EX-202602-SA-15</t>
+          <t>EX-202601-OP-01</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46056</v>
+        <v>46037</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slack</t>
+          <t>Fast Campus</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>838000</v>
+        <v>1619000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1357,45 +1357,45 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>S125</t>
+          <t>O142</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
+          <t>data\inbox\2026-01_operations_expenses.xlsx</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EX-202603-MA-14</t>
+          <t>EX-202602-SA-11</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46104</v>
+        <v>46078</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kakao T</t>
+          <t>DataCloud Korea</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>314000</v>
+        <v>373000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1404,92 +1404,92 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M102</t>
+          <t>S133</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>data\inbox\2026-03_marketing_expenses.xlsx</t>
+          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EX-202603-MA-15</t>
+          <t>EX-202602-SA-14</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46097</v>
+        <v>46059</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kakao T</t>
+          <t>DataCloud Korea</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>394000</v>
+        <v>452000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M112</t>
+          <t>S129</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>data\inbox\2026-03_marketing_expenses.xlsx</t>
+          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EX-202603-OP-01</t>
+          <t>EX-202602-SA-15</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46103</v>
+        <v>46056</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coupang Business</t>
+          <t>Slack</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>224000</v>
+        <v>838000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1498,23 +1498,23 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O146</t>
+          <t>S125</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>data\inbox\2026-03_operations_expenses.xlsx</t>
+          <t>data\inbox\2026-02_sales_expenses.xlsx</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EX-202603-OP-09</t>
+          <t>EX-202603-MA-14</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1522,21 +1522,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coursera</t>
+          <t>Kakao T</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1090000</v>
+        <v>314000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>O153</t>
+          <t>M102</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data\inbox\2026-03_operations_expenses.xlsx</t>
+          <t>data\inbox\2026-03_marketing_expenses.xlsx</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1561,76 +1561,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EX-202604-HR-02</t>
+          <t>EX-202603-MA-15</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46137</v>
+        <v>46097</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Recruiting</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wanted</t>
+          <t>Kakao T</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2151000</v>
+        <v>394000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>H164</t>
+          <t>M112</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
+          <t>data\inbox\2026-03_marketing_expenses.xlsx</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EX-202604-HR-04</t>
+          <t>EX-202603-OP-01</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46115</v>
+        <v>46103</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Korea Management Institute</t>
+          <t>Coupang Business</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1826000</v>
+        <v>224000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1639,31 +1639,31 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>H161</t>
+          <t>O146</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
+          <t>data\inbox\2026-03_operations_expenses.xlsx</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EX-202604-HR-11</t>
+          <t>EX-202603-OP-09</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46119</v>
+        <v>46104</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1673,11 +1673,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fast Campus</t>
+          <t>Coursera</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>620000</v>
+        <v>1090000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1686,45 +1686,45 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>H169</t>
+          <t>O153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
+          <t>data\inbox\2026-03_operations_expenses.xlsx</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EX-202605-MA-24</t>
+          <t>EX-202604-HR-02</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46164</v>
+        <v>46137</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Recruiting</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Wanted</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>200000</v>
+        <v>2151000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1733,44 +1733,46 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M115</t>
+          <t>H164</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>data\inbox\2026-05_marketing_expenses.xlsx</t>
+          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EX-202605-OP-06</t>
+          <t>EX-202604-HR-04</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46152</v>
+        <v>46115</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quick Service Seoul</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>Korea Management Institute</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1826000</v>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -1778,68 +1780,301 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>O148</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Logistics expense</t>
-        </is>
-      </c>
+          <t>H161</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>data\inbox\2026-05_operations_expenses.xlsx</t>
+          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EX-202605-OP-15</t>
+          <t>EX-202604-HR-11</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DataCloud Korea</t>
+          <t>Fast Campus</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>761000</v>
+        <v>620000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>O157</t>
+          <t>H169</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
+          <t>data\inbox\2026-04_hr_expenses.xlsx</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EX-202605-MA-24</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>M115</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>data\inbox\2026-05_marketing_expenses.xlsx</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EX-202605-OP-06</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Quick Service Seoul</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O148</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Logistics expense</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>data\inbox\2026-05_operations_expenses.xlsx</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="K32" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EX-202605-OP-15</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DataCloud Korea</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>761000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O157</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>data\inbox\2026-05_operations_expenses.xlsx</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EX-202606-HR-15</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Meals</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Office Cafe</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>57000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>H168</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>data\inbox\2026-06_hr_expenses.xlsx</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EX-202606-SA-17</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Slack</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>591000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>S128</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>data\inbox\2026-06_sales_expenses.xlsx</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
